--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2022_biobio.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">Tucapel</t>
   </si>
   <si>
+    <t xml:space="preserve">Arauco</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Rosendo</t>
   </si>
   <si>
-    <t xml:space="preserve">Arauco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Alamos</t>
   </si>
   <si>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:22</t>
+    <t xml:space="preserve">2026-09-10 00:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -744,7 +744,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>8310</v>
+        <v>8202</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
@@ -761,7 +761,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>8202</v>
+        <v>8310</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>

--- a/output/graficos_dimensiones/comunal_e_basbrut_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_basbrut_a_2022_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:27</t>
+    <t xml:space="preserve">2026-09-18 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
